--- a/sites.xlsx
+++ b/sites.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="273">
   <si>
     <t>site_name</t>
   </si>
@@ -370,7 +370,7 @@
     <t>63.USITC News</t>
   </si>
   <si>
-    <t>https://www.gov.br/planalto/en/latest-news</t>
+    <t>https://www.gov.br/receitafederal/pt-br/assuntos/noticias</t>
   </si>
   <si>
     <t>http://english.customs.gov.cn/newsroom/news</t>
@@ -799,34 +799,31 @@
     <t>customs_tax</t>
   </si>
   <si>
+    <t>NO_NEW</t>
+  </si>
+  <si>
     <t>OK</t>
   </si>
   <si>
     <t>CHECK</t>
   </si>
   <si>
-    <t>NO_NEW</t>
-  </si>
-  <si>
-    <t>FAIL</t>
+    <t>STEP1</t>
   </si>
   <si>
     <t>STEP2-3</t>
   </si>
   <si>
-    <t>STEP1</t>
+    <t>Y</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>Y</t>
+    <t>CORE</t>
   </si>
   <si>
     <t>WATCH</t>
-  </si>
-  <si>
-    <t>CORE</t>
   </si>
   <si>
     <t>NEW</t>
@@ -1299,37 +1296,40 @@
         <v>1</v>
       </c>
       <c r="J2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K2">
         <v>1855</v>
       </c>
       <c r="L2" s="2">
-        <v>46243.50512731481</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M2" t="s">
         <v>261</v>
       </c>
       <c r="N2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="R2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="W2" s="2">
         <v>46155</v>
       </c>
       <c r="X2">
         <v>1</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:27">
@@ -1361,37 +1361,40 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K3">
         <v>1812</v>
       </c>
       <c r="L3" s="2">
-        <v>46243.50516203704</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M3" t="s">
         <v>261</v>
       </c>
       <c r="N3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="R3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="W3" s="2">
         <v>46087</v>
       </c>
       <c r="X3">
         <v>2</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:27">
@@ -1432,7 +1435,7 @@
         <v>46243.50517361111</v>
       </c>
       <c r="M4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N4" t="s">
         <v>257</v>
@@ -1494,7 +1497,7 @@
         <v>46243.50518518518</v>
       </c>
       <c r="M5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N5" t="s">
         <v>257</v>
@@ -1553,25 +1556,25 @@
         <v>169</v>
       </c>
       <c r="L6" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M6" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N6" t="s">
         <v>256</v>
       </c>
       <c r="O6" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P6" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q6" t="s">
         <v>268</v>
       </c>
-      <c r="Q6" t="s">
-        <v>270</v>
-      </c>
       <c r="R6" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W6" s="2">
         <v>46168</v>
@@ -1580,13 +1583,13 @@
         <v>5</v>
       </c>
       <c r="Y6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z6" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA6" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7" spans="1:27">
@@ -1627,7 +1630,7 @@
         <v>46243.50520833334</v>
       </c>
       <c r="M7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N7" t="s">
         <v>257</v>
@@ -1689,7 +1692,7 @@
         <v>46243.50521990741</v>
       </c>
       <c r="M8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N8" t="s">
         <v>257</v>
@@ -1742,37 +1745,40 @@
         <v>1</v>
       </c>
       <c r="J9">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K9">
         <v>1961</v>
       </c>
       <c r="L9" s="2">
-        <v>46243.50527777777</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M9" t="s">
         <v>261</v>
       </c>
       <c r="N9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="R9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="W9" s="2">
         <v>46045</v>
       </c>
       <c r="X9">
         <v>8</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:27">
@@ -1804,37 +1810,40 @@
         <v>1</v>
       </c>
       <c r="J10">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K10">
         <v>1764</v>
       </c>
       <c r="L10" s="2">
-        <v>46243.50550925926</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M10" t="s">
         <v>261</v>
       </c>
       <c r="N10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P10" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="R10" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="W10" s="2">
         <v>46045</v>
       </c>
       <c r="X10">
         <v>9</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:27">
@@ -1866,37 +1875,40 @@
         <v>1</v>
       </c>
       <c r="J11">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K11">
         <v>1735</v>
       </c>
       <c r="L11" s="2">
-        <v>46243.50556712963</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M11" t="s">
         <v>261</v>
       </c>
       <c r="N11" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="R11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="W11" s="2">
         <v>46129</v>
       </c>
       <c r="X11">
         <v>10</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="12" spans="1:27">
@@ -1928,37 +1940,40 @@
         <v>1</v>
       </c>
       <c r="J12">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K12">
         <v>417</v>
       </c>
       <c r="L12" s="2">
-        <v>46243.50557870371</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M12" t="s">
         <v>261</v>
       </c>
       <c r="N12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P12" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q12" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="R12" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="W12" s="2">
         <v>46164</v>
       </c>
       <c r="X12">
         <v>11</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:27">
@@ -1996,25 +2011,25 @@
         <v>179</v>
       </c>
       <c r="L13" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M13" t="s">
+        <v>261</v>
+      </c>
+      <c r="N13" t="s">
+        <v>256</v>
+      </c>
+      <c r="O13" t="s">
         <v>264</v>
       </c>
-      <c r="N13" t="s">
-        <v>256</v>
-      </c>
-      <c r="O13" t="s">
-        <v>266</v>
-      </c>
       <c r="P13" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q13" t="s">
         <v>268</v>
       </c>
-      <c r="Q13" t="s">
-        <v>270</v>
-      </c>
       <c r="R13" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W13" s="2">
         <v>46308</v>
@@ -2023,9 +2038,12 @@
         <v>12</v>
       </c>
       <c r="Y13" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z13" t="s">
+        <v>270</v>
+      </c>
+      <c r="AA13" t="s">
         <v>271</v>
       </c>
     </row>
@@ -2061,40 +2079,40 @@
         <v>3</v>
       </c>
       <c r="K14">
-        <v>3578</v>
+        <v>3581</v>
       </c>
       <c r="L14" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N14" t="s">
         <v>256</v>
       </c>
       <c r="O14" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P14" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q14" t="s">
         <v>268</v>
       </c>
-      <c r="Q14" t="s">
-        <v>270</v>
-      </c>
       <c r="R14" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W14" s="2">
         <v>46307</v>
       </c>
       <c r="Y14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z14" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA14" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="15" spans="1:27">
@@ -2129,40 +2147,40 @@
         <v>1</v>
       </c>
       <c r="K15">
-        <v>3553</v>
+        <v>3554</v>
       </c>
       <c r="L15" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M15" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N15" t="s">
         <v>256</v>
       </c>
       <c r="O15" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P15" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q15" t="s">
         <v>268</v>
       </c>
-      <c r="Q15" t="s">
-        <v>270</v>
-      </c>
       <c r="R15" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W15" s="2">
         <v>46304</v>
       </c>
       <c r="Y15" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z15" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA15" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="16" spans="1:27">
@@ -2194,43 +2212,43 @@
         <v>1</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16">
         <v>3609</v>
       </c>
       <c r="L16" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N16" t="s">
         <v>256</v>
       </c>
       <c r="O16" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P16" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q16" t="s">
         <v>268</v>
       </c>
-      <c r="Q16" t="s">
-        <v>270</v>
-      </c>
       <c r="R16" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W16" s="2">
         <v>46308</v>
       </c>
       <c r="Y16" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z16" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA16" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="17" spans="1:27">
@@ -2262,34 +2280,37 @@
         <v>1</v>
       </c>
       <c r="J17">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K17">
         <v>1869</v>
       </c>
       <c r="L17" s="2">
-        <v>46243.50569444444</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M17" t="s">
         <v>261</v>
       </c>
       <c r="N17" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O17" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P17" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q17" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="R17" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="W17" s="2">
         <v>46113</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="18" spans="1:27">
@@ -2321,43 +2342,43 @@
         <v>1</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18">
         <v>3652</v>
       </c>
       <c r="L18" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M18" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N18" t="s">
         <v>256</v>
       </c>
       <c r="O18" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P18" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q18" t="s">
         <v>268</v>
       </c>
-      <c r="Q18" t="s">
-        <v>270</v>
-      </c>
       <c r="R18" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W18" s="2">
         <v>46306</v>
       </c>
       <c r="Y18" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z18" t="s">
+        <v>270</v>
+      </c>
+      <c r="AA18" t="s">
         <v>271</v>
-      </c>
-      <c r="AA18" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="19" spans="1:27">
@@ -2389,34 +2410,37 @@
         <v>1</v>
       </c>
       <c r="J19">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K19">
         <v>125</v>
       </c>
       <c r="L19" s="2">
-        <v>46243.50572916667</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M19" t="s">
         <v>261</v>
       </c>
       <c r="N19" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O19" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P19" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q19" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="R19" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="W19" s="2">
         <v>46163</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="20" spans="1:27">
@@ -2457,7 +2481,7 @@
         <v>46243.50575231481</v>
       </c>
       <c r="M20" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N20" t="s">
         <v>257</v>
@@ -2516,7 +2540,7 @@
         <v>46243.50576388889</v>
       </c>
       <c r="M21" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N21" t="s">
         <v>257</v>
@@ -2572,37 +2596,37 @@
         <v>3591</v>
       </c>
       <c r="L22" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M22" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N22" t="s">
         <v>256</v>
       </c>
       <c r="O22" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P22" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q22" t="s">
         <v>268</v>
       </c>
-      <c r="Q22" t="s">
-        <v>270</v>
-      </c>
       <c r="R22" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W22" s="2">
         <v>46168</v>
       </c>
       <c r="Y22" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z22" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA22" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="23" spans="1:27">
@@ -2640,37 +2664,37 @@
         <v>3591</v>
       </c>
       <c r="L23" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M23" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N23" t="s">
         <v>256</v>
       </c>
       <c r="O23" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P23" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q23" t="s">
         <v>268</v>
       </c>
-      <c r="Q23" t="s">
-        <v>270</v>
-      </c>
       <c r="R23" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W23" s="2">
         <v>46168</v>
       </c>
       <c r="Y23" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z23" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA23" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="24" spans="1:27">
@@ -2708,37 +2732,37 @@
         <v>142</v>
       </c>
       <c r="L24" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M24" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N24" t="s">
         <v>256</v>
       </c>
       <c r="O24" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P24" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q24" t="s">
         <v>268</v>
       </c>
-      <c r="Q24" t="s">
-        <v>270</v>
-      </c>
       <c r="R24" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W24" s="2">
         <v>46302</v>
       </c>
       <c r="Y24" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z24" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA24" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="25" spans="1:27">
@@ -2770,43 +2794,43 @@
         <v>1</v>
       </c>
       <c r="J25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K25">
         <v>164</v>
       </c>
       <c r="L25" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M25" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N25" t="s">
         <v>256</v>
       </c>
       <c r="O25" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P25" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q25" t="s">
         <v>268</v>
       </c>
-      <c r="Q25" t="s">
-        <v>270</v>
-      </c>
       <c r="R25" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W25" s="2">
         <v>46307</v>
       </c>
       <c r="Y25" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z25" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA25" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="26" spans="1:27">
@@ -2841,40 +2865,40 @@
         <v>1</v>
       </c>
       <c r="K26">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L26" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M26" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N26" t="s">
         <v>256</v>
       </c>
       <c r="O26" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P26" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q26" t="s">
         <v>268</v>
       </c>
-      <c r="Q26" t="s">
-        <v>270</v>
-      </c>
       <c r="R26" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W26" s="2">
         <v>46307</v>
       </c>
       <c r="Y26" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z26" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA26" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="27" spans="1:27">
@@ -2906,34 +2930,37 @@
         <v>1</v>
       </c>
       <c r="J27">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K27">
         <v>2226</v>
       </c>
       <c r="L27" s="2">
-        <v>46243.50589120371</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M27" t="s">
         <v>261</v>
       </c>
       <c r="N27" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O27" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P27" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q27" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="R27" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="W27" s="2">
         <v>46172</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="28" spans="1:27">
@@ -2965,34 +2992,37 @@
         <v>1</v>
       </c>
       <c r="J28">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K28">
         <v>2264</v>
       </c>
       <c r="L28" s="2">
-        <v>46243.50591435185</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M28" t="s">
         <v>261</v>
       </c>
       <c r="N28" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O28" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P28" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q28" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="R28" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="W28" s="2">
         <v>46164</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="29" spans="1:27">
@@ -3024,34 +3054,37 @@
         <v>1</v>
       </c>
       <c r="J29">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="K29">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="L29" s="2">
-        <v>46243.50592592593</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M29" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N29" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O29" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P29" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q29" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="R29" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="W29" s="2">
-        <v>46168</v>
+        <v>46303.5896875</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="30" spans="1:27">
@@ -3092,7 +3125,7 @@
         <v>46243.50594907408</v>
       </c>
       <c r="M30" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N30" t="s">
         <v>257</v>
@@ -3151,7 +3184,7 @@
         <v>46243.50596064814</v>
       </c>
       <c r="M31" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N31" t="s">
         <v>257</v>
@@ -3201,43 +3234,43 @@
         <v>1</v>
       </c>
       <c r="J32">
-        <v>166</v>
+        <v>93</v>
       </c>
       <c r="K32">
-        <v>16446</v>
+        <v>16539</v>
       </c>
       <c r="L32" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M32" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N32" t="s">
         <v>256</v>
       </c>
       <c r="O32" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P32" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q32" t="s">
         <v>268</v>
       </c>
-      <c r="Q32" t="s">
+      <c r="R32" t="s">
+        <v>266</v>
+      </c>
+      <c r="W32" s="2">
+        <v>46309</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>262</v>
+      </c>
+      <c r="Z32" t="s">
         <v>270</v>
       </c>
-      <c r="R32" t="s">
-        <v>268</v>
-      </c>
-      <c r="W32" s="2">
-        <v>46308</v>
-      </c>
-      <c r="Y32" t="s">
-        <v>261</v>
-      </c>
-      <c r="Z32" t="s">
+      <c r="AA32" t="s">
         <v>271</v>
-      </c>
-      <c r="AA32" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="33" spans="1:27">
@@ -3278,7 +3311,7 @@
         <v>46243.50614583334</v>
       </c>
       <c r="M33" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N33" t="s">
         <v>257</v>
@@ -3337,7 +3370,7 @@
         <v>46243.50615740741</v>
       </c>
       <c r="M34" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N34" t="s">
         <v>257</v>
@@ -3393,37 +3426,37 @@
         <v>3591</v>
       </c>
       <c r="L35" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M35" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N35" t="s">
         <v>256</v>
       </c>
       <c r="O35" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P35" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q35" t="s">
         <v>268</v>
       </c>
-      <c r="Q35" t="s">
-        <v>270</v>
-      </c>
       <c r="R35" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W35" s="2">
         <v>46157</v>
       </c>
       <c r="Y35" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z35" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA35" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="36" spans="1:27">
@@ -3461,37 +3494,37 @@
         <v>3591</v>
       </c>
       <c r="L36" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M36" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N36" t="s">
         <v>256</v>
       </c>
       <c r="O36" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P36" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q36" t="s">
         <v>268</v>
       </c>
-      <c r="Q36" t="s">
-        <v>270</v>
-      </c>
       <c r="R36" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W36" s="2">
         <v>46168</v>
       </c>
       <c r="Y36" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z36" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA36" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="37" spans="1:27">
@@ -3529,37 +3562,37 @@
         <v>1827</v>
       </c>
       <c r="L37" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M37" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N37" t="s">
         <v>256</v>
       </c>
       <c r="O37" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P37" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q37" t="s">
         <v>268</v>
       </c>
-      <c r="Q37" t="s">
-        <v>270</v>
-      </c>
       <c r="R37" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W37" s="2">
         <v>46285</v>
       </c>
       <c r="Y37" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z37" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="38" spans="1:27">
@@ -3597,37 +3630,37 @@
         <v>2937</v>
       </c>
       <c r="L38" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M38" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N38" t="s">
         <v>256</v>
       </c>
       <c r="O38" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P38" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q38" t="s">
         <v>268</v>
       </c>
-      <c r="Q38" t="s">
-        <v>270</v>
-      </c>
       <c r="R38" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W38" s="2">
         <v>46113</v>
       </c>
       <c r="Y38" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z38" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA38" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="39" spans="1:27">
@@ -3665,37 +3698,37 @@
         <v>3176</v>
       </c>
       <c r="L39" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M39" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N39" t="s">
         <v>256</v>
       </c>
       <c r="O39" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P39" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q39" t="s">
         <v>268</v>
       </c>
-      <c r="Q39" t="s">
-        <v>270</v>
-      </c>
       <c r="R39" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W39" s="2">
         <v>46140</v>
       </c>
       <c r="Y39" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z39" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA39" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="40" spans="1:27">
@@ -3733,37 +3766,37 @@
         <v>3128</v>
       </c>
       <c r="L40" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M40" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N40" t="s">
         <v>256</v>
       </c>
       <c r="O40" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P40" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q40" t="s">
         <v>268</v>
       </c>
-      <c r="Q40" t="s">
-        <v>270</v>
-      </c>
       <c r="R40" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W40" s="2">
         <v>46024</v>
       </c>
       <c r="Y40" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z40" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA40" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="41" spans="1:27">
@@ -3801,37 +3834,37 @@
         <v>3542</v>
       </c>
       <c r="L41" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M41" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N41" t="s">
         <v>256</v>
       </c>
       <c r="O41" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P41" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q41" t="s">
         <v>268</v>
       </c>
-      <c r="Q41" t="s">
-        <v>270</v>
-      </c>
       <c r="R41" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W41" s="2">
         <v>46168</v>
       </c>
       <c r="Y41" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z41" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA41" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="42" spans="1:27">
@@ -3869,37 +3902,37 @@
         <v>3533</v>
       </c>
       <c r="L42" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M42" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N42" t="s">
         <v>256</v>
       </c>
       <c r="O42" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P42" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q42" t="s">
         <v>268</v>
       </c>
-      <c r="Q42" t="s">
-        <v>270</v>
-      </c>
       <c r="R42" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W42" s="2">
         <v>46164</v>
       </c>
       <c r="Y42" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z42" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA42" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="43" spans="1:27">
@@ -3937,37 +3970,37 @@
         <v>3513</v>
       </c>
       <c r="L43" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M43" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N43" t="s">
         <v>256</v>
       </c>
       <c r="O43" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P43" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q43" t="s">
         <v>268</v>
       </c>
-      <c r="Q43" t="s">
-        <v>270</v>
-      </c>
       <c r="R43" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W43" s="2">
         <v>46112</v>
       </c>
       <c r="Y43" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z43" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA43" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="44" spans="1:27">
@@ -4008,7 +4041,7 @@
         <v>46243.50630787037</v>
       </c>
       <c r="M44" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N44" t="s">
         <v>257</v>
@@ -4061,40 +4094,40 @@
         <v>10</v>
       </c>
       <c r="K45">
-        <v>3903</v>
+        <v>3913</v>
       </c>
       <c r="L45" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M45" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N45" t="s">
         <v>256</v>
       </c>
       <c r="O45" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P45" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q45" t="s">
         <v>268</v>
       </c>
-      <c r="Q45" t="s">
-        <v>270</v>
-      </c>
       <c r="R45" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W45" s="2">
         <v>46308</v>
       </c>
       <c r="Y45" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z45" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA45" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="46" spans="1:27">
@@ -4126,43 +4159,43 @@
         <v>1</v>
       </c>
       <c r="J46">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K46">
-        <v>10483</v>
+        <v>10508</v>
       </c>
       <c r="L46" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M46" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N46" t="s">
         <v>256</v>
       </c>
       <c r="O46" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P46" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q46" t="s">
         <v>268</v>
       </c>
-      <c r="Q46" t="s">
-        <v>270</v>
-      </c>
       <c r="R46" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W46" s="2">
         <v>46308</v>
       </c>
       <c r="Y46" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z46" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA46" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="47" spans="1:27">
@@ -4197,40 +4230,40 @@
         <v>17</v>
       </c>
       <c r="K47">
-        <v>4899</v>
+        <v>4916</v>
       </c>
       <c r="L47" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M47" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N47" t="s">
         <v>256</v>
       </c>
       <c r="O47" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P47" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q47" t="s">
         <v>268</v>
       </c>
-      <c r="Q47" t="s">
-        <v>270</v>
-      </c>
       <c r="R47" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W47" s="2">
         <v>46308</v>
       </c>
       <c r="Y47" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z47" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA47" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="48" spans="1:27">
@@ -4268,37 +4301,37 @@
         <v>2299</v>
       </c>
       <c r="L48" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M48" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N48" t="s">
         <v>256</v>
       </c>
       <c r="O48" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P48" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q48" t="s">
         <v>268</v>
       </c>
-      <c r="Q48" t="s">
-        <v>270</v>
-      </c>
       <c r="R48" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W48" s="2">
         <v>46168</v>
       </c>
       <c r="Y48" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z48" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA48" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="49" spans="1:27">
@@ -4336,37 +4369,37 @@
         <v>1515</v>
       </c>
       <c r="L49" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M49" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N49" t="s">
         <v>256</v>
       </c>
       <c r="O49" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P49" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q49" t="s">
         <v>268</v>
       </c>
-      <c r="Q49" t="s">
-        <v>270</v>
-      </c>
       <c r="R49" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W49" s="2">
         <v>46288</v>
       </c>
       <c r="Y49" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z49" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA49" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="50" spans="1:27">
@@ -4398,43 +4431,43 @@
         <v>1</v>
       </c>
       <c r="J50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K50">
-        <v>1789</v>
+        <v>1793</v>
       </c>
       <c r="L50" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M50" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N50" t="s">
         <v>256</v>
       </c>
       <c r="O50" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P50" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q50" t="s">
         <v>268</v>
       </c>
-      <c r="Q50" t="s">
-        <v>270</v>
-      </c>
       <c r="R50" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W50" s="2">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="Y50" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z50" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA50" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="51" spans="1:27">
@@ -4466,13 +4499,13 @@
         <v>1</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="L51" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M51" t="s">
         <v>263</v>
@@ -4481,28 +4514,28 @@
         <v>256</v>
       </c>
       <c r="O51" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P51" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q51" t="s">
         <v>268</v>
       </c>
-      <c r="Q51" t="s">
-        <v>270</v>
-      </c>
       <c r="R51" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W51" s="2">
-        <v>46293</v>
+        <v>46307</v>
       </c>
       <c r="Y51" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z51" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA51" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="52" spans="1:27">
@@ -4534,43 +4567,43 @@
         <v>1</v>
       </c>
       <c r="J52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52">
         <v>1473</v>
       </c>
       <c r="L52" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M52" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N52" t="s">
         <v>256</v>
       </c>
       <c r="O52" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P52" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q52" t="s">
         <v>268</v>
       </c>
-      <c r="Q52" t="s">
-        <v>270</v>
-      </c>
       <c r="R52" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W52" s="2">
         <v>46306</v>
       </c>
       <c r="Y52" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z52" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA52" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="53" spans="1:27">
@@ -4608,37 +4641,37 @@
         <v>2217</v>
       </c>
       <c r="L53" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M53" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N53" t="s">
         <v>256</v>
       </c>
       <c r="O53" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P53" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q53" t="s">
         <v>268</v>
       </c>
-      <c r="Q53" t="s">
-        <v>270</v>
-      </c>
       <c r="R53" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W53" s="2">
         <v>46302</v>
       </c>
       <c r="Y53" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z53" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA53" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="54" spans="1:27">
@@ -4676,37 +4709,37 @@
         <v>1396</v>
       </c>
       <c r="L54" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M54" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N54" t="s">
         <v>256</v>
       </c>
       <c r="O54" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P54" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q54" t="s">
         <v>268</v>
       </c>
-      <c r="Q54" t="s">
-        <v>270</v>
-      </c>
       <c r="R54" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W54" s="2">
         <v>46302</v>
       </c>
       <c r="Y54" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z54" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA54" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="55" spans="1:27">
@@ -4738,43 +4771,43 @@
         <v>1</v>
       </c>
       <c r="J55">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K55">
-        <v>2563</v>
+        <v>2564</v>
       </c>
       <c r="L55" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M55" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N55" t="s">
         <v>256</v>
       </c>
       <c r="O55" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P55" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q55" t="s">
         <v>268</v>
       </c>
-      <c r="Q55" t="s">
-        <v>270</v>
-      </c>
       <c r="R55" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W55" s="2">
         <v>46308</v>
       </c>
       <c r="Y55" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z55" t="s">
+        <v>270</v>
+      </c>
+      <c r="AA55" t="s">
         <v>271</v>
-      </c>
-      <c r="AA55" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="56" spans="1:27">
@@ -4815,7 +4848,7 @@
         <v>46243.50703703704</v>
       </c>
       <c r="M56" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N56" t="s">
         <v>257</v>
@@ -4865,43 +4898,43 @@
         <v>1</v>
       </c>
       <c r="J57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K57">
-        <v>4011</v>
+        <v>4012</v>
       </c>
       <c r="L57" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M57" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N57" t="s">
         <v>256</v>
       </c>
       <c r="O57" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P57" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q57" t="s">
         <v>268</v>
       </c>
-      <c r="Q57" t="s">
-        <v>270</v>
-      </c>
       <c r="R57" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W57" s="2">
         <v>46307</v>
       </c>
       <c r="Y57" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z57" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA57" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="58" spans="1:27">
@@ -4942,7 +4975,7 @@
         <v>46243.50706018518</v>
       </c>
       <c r="M58" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N58" t="s">
         <v>257</v>
@@ -5001,7 +5034,7 @@
         <v>46243.50706018518</v>
       </c>
       <c r="M59" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N59" t="s">
         <v>257</v>
@@ -5060,7 +5093,7 @@
         <v>46243.50707175926</v>
       </c>
       <c r="M60" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N60" t="s">
         <v>257</v>
@@ -5119,7 +5152,7 @@
         <v>46243.50708333333</v>
       </c>
       <c r="M61" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N61" t="s">
         <v>257</v>
@@ -5175,37 +5208,37 @@
         <v>1681</v>
       </c>
       <c r="L62" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M62" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N62" t="s">
         <v>256</v>
       </c>
       <c r="O62" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P62" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q62" t="s">
         <v>268</v>
       </c>
-      <c r="Q62" t="s">
-        <v>270</v>
-      </c>
       <c r="R62" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W62" s="2">
         <v>46288</v>
       </c>
       <c r="Y62" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z62" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA62" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="63" spans="1:27">
@@ -5246,7 +5279,7 @@
         <v>46243.50712962963</v>
       </c>
       <c r="M63" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N63" t="s">
         <v>257</v>
@@ -5305,7 +5338,7 @@
         <v>46243.50715277778</v>
       </c>
       <c r="M64" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N64" t="s">
         <v>257</v>
@@ -5317,10 +5350,10 @@
         <v>267</v>
       </c>
       <c r="Q64" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="R64" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W64" s="2">
         <v>46168</v>
@@ -5355,43 +5388,43 @@
         <v>1</v>
       </c>
       <c r="J65">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="K65">
-        <v>4953</v>
+        <v>4963</v>
       </c>
       <c r="L65" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M65" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N65" t="s">
         <v>256</v>
       </c>
       <c r="O65" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P65" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q65" t="s">
         <v>268</v>
       </c>
-      <c r="Q65" t="s">
-        <v>270</v>
-      </c>
       <c r="R65" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W65" s="2">
         <v>46308</v>
       </c>
       <c r="Y65" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z65" t="s">
+        <v>270</v>
+      </c>
+      <c r="AA65" t="s">
         <v>271</v>
-      </c>
-      <c r="AA65" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="66" spans="1:27">
@@ -5429,37 +5462,37 @@
         <v>3062</v>
       </c>
       <c r="L66" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M66" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N66" t="s">
         <v>256</v>
       </c>
       <c r="O66" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P66" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q66" t="s">
         <v>268</v>
       </c>
-      <c r="Q66" t="s">
-        <v>270</v>
-      </c>
       <c r="R66" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W66" s="2">
         <v>46261</v>
       </c>
       <c r="Y66" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z66" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA66" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="67" spans="1:27">
@@ -5494,40 +5527,40 @@
         <v>1</v>
       </c>
       <c r="K67">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="L67" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M67" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N67" t="s">
         <v>256</v>
       </c>
       <c r="O67" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P67" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q67" t="s">
         <v>268</v>
       </c>
-      <c r="Q67" t="s">
-        <v>270</v>
-      </c>
       <c r="R67" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W67" s="2">
         <v>46308</v>
       </c>
       <c r="Y67" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z67" t="s">
+        <v>270</v>
+      </c>
+      <c r="AA67" t="s">
         <v>271</v>
-      </c>
-      <c r="AA67" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="68" spans="1:27">
@@ -5559,43 +5592,43 @@
         <v>1</v>
       </c>
       <c r="J68">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="K68">
-        <v>4523</v>
+        <v>4529</v>
       </c>
       <c r="L68" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M68" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N68" t="s">
         <v>256</v>
       </c>
       <c r="O68" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P68" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q68" t="s">
         <v>268</v>
       </c>
-      <c r="Q68" t="s">
+      <c r="R68" t="s">
+        <v>266</v>
+      </c>
+      <c r="W68" s="2">
+        <v>46309</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>262</v>
+      </c>
+      <c r="Z68" t="s">
         <v>270</v>
       </c>
-      <c r="R68" t="s">
-        <v>268</v>
-      </c>
-      <c r="W68" s="2">
-        <v>46308</v>
-      </c>
-      <c r="Y68" t="s">
-        <v>261</v>
-      </c>
-      <c r="Z68" t="s">
+      <c r="AA68" t="s">
         <v>271</v>
-      </c>
-      <c r="AA68" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="69" spans="1:27">
@@ -5633,37 +5666,37 @@
         <v>3069</v>
       </c>
       <c r="L69" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M69" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N69" t="s">
         <v>256</v>
       </c>
       <c r="O69" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P69" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q69" t="s">
         <v>268</v>
       </c>
-      <c r="Q69" t="s">
-        <v>270</v>
-      </c>
       <c r="R69" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W69" s="2">
         <v>46280</v>
       </c>
       <c r="Y69" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z69" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA69" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="70" spans="1:27">
@@ -5695,43 +5728,43 @@
         <v>1</v>
       </c>
       <c r="J70">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K70">
-        <v>2823</v>
+        <v>2827</v>
       </c>
       <c r="L70" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M70" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N70" t="s">
         <v>256</v>
       </c>
       <c r="O70" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P70" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q70" t="s">
         <v>268</v>
       </c>
-      <c r="Q70" t="s">
+      <c r="R70" t="s">
+        <v>266</v>
+      </c>
+      <c r="W70" s="2">
+        <v>46309</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>262</v>
+      </c>
+      <c r="Z70" t="s">
         <v>270</v>
       </c>
-      <c r="R70" t="s">
-        <v>268</v>
-      </c>
-      <c r="W70" s="2">
-        <v>46308</v>
-      </c>
-      <c r="Y70" t="s">
-        <v>261</v>
-      </c>
-      <c r="Z70" t="s">
+      <c r="AA70" t="s">
         <v>271</v>
-      </c>
-      <c r="AA70" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="71" spans="1:27">
@@ -5763,43 +5796,43 @@
         <v>1</v>
       </c>
       <c r="J71">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K71">
-        <v>2851</v>
+        <v>2854</v>
       </c>
       <c r="L71" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M71" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N71" t="s">
         <v>256</v>
       </c>
       <c r="O71" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P71" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q71" t="s">
         <v>268</v>
       </c>
-      <c r="Q71" t="s">
-        <v>270</v>
-      </c>
       <c r="R71" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W71" s="2">
         <v>46308</v>
       </c>
       <c r="Y71" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z71" t="s">
+        <v>270</v>
+      </c>
+      <c r="AA71" t="s">
         <v>271</v>
-      </c>
-      <c r="AA71" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="72" spans="1:27">
@@ -5840,7 +5873,7 @@
         <v>46243.50783564815</v>
       </c>
       <c r="M72" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N72" t="s">
         <v>257</v>
@@ -5896,37 +5929,37 @@
         <v>1393</v>
       </c>
       <c r="L73" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M73" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N73" t="s">
         <v>256</v>
       </c>
       <c r="O73" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P73" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q73" t="s">
         <v>268</v>
       </c>
-      <c r="Q73" t="s">
-        <v>270</v>
-      </c>
       <c r="R73" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W73" s="2">
         <v>46301</v>
       </c>
       <c r="Y73" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z73" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA73" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="74" spans="1:27">
@@ -5964,37 +5997,37 @@
         <v>1449</v>
       </c>
       <c r="L74" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M74" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N74" t="s">
         <v>256</v>
       </c>
       <c r="O74" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P74" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q74" t="s">
         <v>268</v>
       </c>
-      <c r="Q74" t="s">
-        <v>270</v>
-      </c>
       <c r="R74" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W74" s="2">
         <v>46185</v>
       </c>
       <c r="Y74" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z74" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA74" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="75" spans="1:27">
@@ -6032,37 +6065,37 @@
         <v>1482</v>
       </c>
       <c r="L75" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M75" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N75" t="s">
         <v>256</v>
       </c>
       <c r="O75" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P75" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q75" t="s">
         <v>268</v>
       </c>
-      <c r="Q75" t="s">
-        <v>270</v>
-      </c>
       <c r="R75" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W75" s="2">
         <v>46265</v>
       </c>
       <c r="Y75" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z75" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA75" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="76" spans="1:27">
@@ -6100,37 +6133,37 @@
         <v>1546</v>
       </c>
       <c r="L76" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M76" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N76" t="s">
         <v>256</v>
       </c>
       <c r="O76" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P76" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q76" t="s">
         <v>268</v>
       </c>
-      <c r="Q76" t="s">
-        <v>270</v>
-      </c>
       <c r="R76" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W76" s="2">
         <v>46303</v>
       </c>
       <c r="Y76" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z76" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA76" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="77" spans="1:27">
@@ -6168,37 +6201,37 @@
         <v>1581</v>
       </c>
       <c r="L77" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M77" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N77" t="s">
         <v>256</v>
       </c>
       <c r="O77" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P77" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q77" t="s">
         <v>268</v>
       </c>
-      <c r="Q77" t="s">
-        <v>270</v>
-      </c>
       <c r="R77" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W77" s="2">
         <v>46301</v>
       </c>
       <c r="Y77" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z77" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA77" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="78" spans="1:27">
@@ -6236,37 +6269,37 @@
         <v>1580</v>
       </c>
       <c r="L78" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M78" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N78" t="s">
         <v>256</v>
       </c>
       <c r="O78" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P78" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q78" t="s">
         <v>268</v>
       </c>
-      <c r="Q78" t="s">
-        <v>270</v>
-      </c>
       <c r="R78" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W78" s="2">
         <v>46288</v>
       </c>
       <c r="Y78" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z78" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA78" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="79" spans="1:27">
@@ -6301,40 +6334,40 @@
         <v>3</v>
       </c>
       <c r="K79">
-        <v>1899</v>
+        <v>1902</v>
       </c>
       <c r="L79" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M79" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N79" t="s">
         <v>256</v>
       </c>
       <c r="O79" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P79" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q79" t="s">
         <v>268</v>
       </c>
-      <c r="Q79" t="s">
-        <v>270</v>
-      </c>
       <c r="R79" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W79" s="2">
         <v>46308</v>
       </c>
       <c r="Y79" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z79" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA79" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="80" spans="1:27">
@@ -6366,43 +6399,43 @@
         <v>1</v>
       </c>
       <c r="J80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K80">
         <v>1632</v>
       </c>
       <c r="L80" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M80" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N80" t="s">
         <v>256</v>
       </c>
       <c r="O80" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P80" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q80" t="s">
         <v>268</v>
       </c>
-      <c r="Q80" t="s">
-        <v>270</v>
-      </c>
       <c r="R80" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W80" s="2">
         <v>46305</v>
       </c>
       <c r="Y80" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z80" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA80" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="81" spans="1:27">
@@ -6440,37 +6473,37 @@
         <v>3591</v>
       </c>
       <c r="L81" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M81" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N81" t="s">
         <v>256</v>
       </c>
       <c r="O81" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P81" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q81" t="s">
         <v>268</v>
       </c>
-      <c r="Q81" t="s">
-        <v>270</v>
-      </c>
       <c r="R81" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W81" s="2">
         <v>46160</v>
       </c>
       <c r="Y81" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z81" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA81" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="82" spans="1:27">
@@ -6502,34 +6535,37 @@
         <v>1</v>
       </c>
       <c r="J82">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K82">
         <v>2137</v>
       </c>
       <c r="L82" s="2">
-        <v>46243.50800925926</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M82" t="s">
         <v>261</v>
       </c>
       <c r="N82" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O82" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P82" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q82" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="R82" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="W82" s="2">
         <v>46161</v>
+      </c>
+      <c r="AA82" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="83" spans="1:27">
@@ -6561,34 +6597,37 @@
         <v>1</v>
       </c>
       <c r="J83">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K83">
         <v>486</v>
       </c>
       <c r="L83" s="2">
-        <v>46243.50802083333</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M83" t="s">
         <v>261</v>
       </c>
       <c r="N83" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O83" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P83" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q83" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="R83" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="W83" s="2">
         <v>46168</v>
+      </c>
+      <c r="AA83" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="84" spans="1:27">
@@ -6629,7 +6668,7 @@
         <v>46243.50803240741</v>
       </c>
       <c r="M84" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N84" t="s">
         <v>257</v>
@@ -6688,7 +6727,7 @@
         <v>46243.50804398148</v>
       </c>
       <c r="M85" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N85" t="s">
         <v>257</v>
@@ -6744,37 +6783,37 @@
         <v>652</v>
       </c>
       <c r="L86" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N86" t="s">
         <v>256</v>
       </c>
       <c r="O86" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P86" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q86" t="s">
         <v>268</v>
       </c>
-      <c r="Q86" t="s">
-        <v>270</v>
-      </c>
       <c r="R86" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W86" s="2">
         <v>46164</v>
       </c>
       <c r="Y86" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA86" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="87" spans="1:27">
@@ -6806,43 +6845,43 @@
         <v>1</v>
       </c>
       <c r="J87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K87">
         <v>3617</v>
       </c>
       <c r="L87" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M87" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N87" t="s">
         <v>256</v>
       </c>
       <c r="O87" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P87" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q87" t="s">
         <v>268</v>
       </c>
-      <c r="Q87" t="s">
-        <v>270</v>
-      </c>
       <c r="R87" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W87" s="2">
         <v>46303</v>
       </c>
       <c r="Y87" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z87" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA87" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="88" spans="1:27">
@@ -6880,37 +6919,37 @@
         <v>3580</v>
       </c>
       <c r="L88" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M88" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N88" t="s">
         <v>256</v>
       </c>
       <c r="O88" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P88" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q88" t="s">
         <v>268</v>
       </c>
-      <c r="Q88" t="s">
-        <v>270</v>
-      </c>
       <c r="R88" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W88" s="2">
         <v>46253.16666666666</v>
       </c>
       <c r="Y88" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z88" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AA88" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="89" spans="1:27">
@@ -6983,40 +7022,43 @@
         <v>1</v>
       </c>
       <c r="J90">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K90">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="L90" s="2">
-        <v>46308.94292824074</v>
+        <v>46309.20672453703</v>
       </c>
       <c r="M90" t="s">
+        <v>262</v>
+      </c>
+      <c r="N90" t="s">
+        <v>256</v>
+      </c>
+      <c r="O90" t="s">
         <v>264</v>
       </c>
-      <c r="N90" t="s">
-        <v>256</v>
-      </c>
-      <c r="O90" t="s">
-        <v>266</v>
-      </c>
       <c r="P90" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q90" t="s">
         <v>268</v>
       </c>
-      <c r="Q90" t="s">
-        <v>270</v>
-      </c>
       <c r="R90" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W90" s="2">
-        <v>46154</v>
+        <v>46304</v>
       </c>
       <c r="Y90" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z90" t="s">
-        <v>263</v>
+        <v>261</v>
+      </c>
+      <c r="AA90" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="91" spans="1:27">
@@ -7048,16 +7090,16 @@
         <v>256</v>
       </c>
       <c r="O91" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P91" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q91" t="s">
         <v>268</v>
       </c>
-      <c r="Q91" t="s">
-        <v>270</v>
-      </c>
       <c r="R91" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W91" s="2">
         <v>46154</v>
@@ -7101,7 +7143,7 @@
         <v>46243.50813657408</v>
       </c>
       <c r="M92" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N92" t="s">
         <v>257</v>

--- a/sites.xlsx
+++ b/sites.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="274">
   <si>
     <t>site_name</t>
   </si>
@@ -808,6 +808,9 @@
     <t>CHECK</t>
   </si>
   <si>
+    <t>CHECK_REQUIRED</t>
+  </si>
+  <si>
     <t>STEP1</t>
   </si>
   <si>
@@ -832,7 +835,7 @@
     <t>PRIMARY_PARSER</t>
   </si>
   <si>
-    <t>selenium:detail_date</t>
+    <t>RECENT_HINT_BUT_ZERO</t>
   </si>
 </sst>
 </file>
@@ -1302,7 +1305,7 @@
         <v>1855</v>
       </c>
       <c r="L2" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29366898148</v>
       </c>
       <c r="M2" t="s">
         <v>261</v>
@@ -1311,16 +1314,16 @@
         <v>256</v>
       </c>
       <c r="O2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W2" s="2">
         <v>46155</v>
@@ -1329,7 +1332,7 @@
         <v>1</v>
       </c>
       <c r="AA2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:27">
@@ -1367,7 +1370,7 @@
         <v>1812</v>
       </c>
       <c r="L3" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29366898148</v>
       </c>
       <c r="M3" t="s">
         <v>261</v>
@@ -1376,16 +1379,16 @@
         <v>256</v>
       </c>
       <c r="O3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W3" s="2">
         <v>46087</v>
@@ -1394,7 +1397,7 @@
         <v>2</v>
       </c>
       <c r="AA3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:27">
@@ -1441,16 +1444,16 @@
         <v>257</v>
       </c>
       <c r="O4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W4" s="2">
         <v>46168</v>
@@ -1503,16 +1506,16 @@
         <v>257</v>
       </c>
       <c r="O5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W5" s="2">
         <v>46161</v>
@@ -1556,7 +1559,7 @@
         <v>169</v>
       </c>
       <c r="L6" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29366898148</v>
       </c>
       <c r="M6" t="s">
         <v>261</v>
@@ -1565,16 +1568,16 @@
         <v>256</v>
       </c>
       <c r="O6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W6" s="2">
         <v>46168</v>
@@ -1636,16 +1639,16 @@
         <v>257</v>
       </c>
       <c r="O7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W7" s="2">
         <v>46164</v>
@@ -1698,16 +1701,16 @@
         <v>257</v>
       </c>
       <c r="O8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W8" s="2">
         <v>46155</v>
@@ -1751,7 +1754,7 @@
         <v>1961</v>
       </c>
       <c r="L9" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29366898148</v>
       </c>
       <c r="M9" t="s">
         <v>261</v>
@@ -1760,16 +1763,16 @@
         <v>256</v>
       </c>
       <c r="O9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W9" s="2">
         <v>46045</v>
@@ -1778,7 +1781,7 @@
         <v>8</v>
       </c>
       <c r="AA9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:27">
@@ -1816,7 +1819,7 @@
         <v>1764</v>
       </c>
       <c r="L10" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29366898148</v>
       </c>
       <c r="M10" t="s">
         <v>261</v>
@@ -1825,16 +1828,16 @@
         <v>256</v>
       </c>
       <c r="O10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W10" s="2">
         <v>46045</v>
@@ -1843,7 +1846,7 @@
         <v>9</v>
       </c>
       <c r="AA10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:27">
@@ -1881,7 +1884,7 @@
         <v>1735</v>
       </c>
       <c r="L11" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29366898148</v>
       </c>
       <c r="M11" t="s">
         <v>261</v>
@@ -1890,16 +1893,16 @@
         <v>256</v>
       </c>
       <c r="O11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P11" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q11" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R11" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W11" s="2">
         <v>46129</v>
@@ -1908,7 +1911,7 @@
         <v>10</v>
       </c>
       <c r="AA11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:27">
@@ -1946,7 +1949,7 @@
         <v>417</v>
       </c>
       <c r="L12" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29366898148</v>
       </c>
       <c r="M12" t="s">
         <v>261</v>
@@ -1955,16 +1958,16 @@
         <v>256</v>
       </c>
       <c r="O12" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P12" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q12" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R12" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W12" s="2">
         <v>46164</v>
@@ -1973,7 +1976,7 @@
         <v>11</v>
       </c>
       <c r="AA12" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:27">
@@ -2011,7 +2014,7 @@
         <v>179</v>
       </c>
       <c r="L13" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29366898148</v>
       </c>
       <c r="M13" t="s">
         <v>261</v>
@@ -2020,16 +2023,16 @@
         <v>256</v>
       </c>
       <c r="O13" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q13" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W13" s="2">
         <v>46308</v>
@@ -2041,10 +2044,10 @@
         <v>262</v>
       </c>
       <c r="Z13" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AA13" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:27">
@@ -2076,31 +2079,31 @@
         <v>1</v>
       </c>
       <c r="J14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K14">
-        <v>3581</v>
+        <v>3599</v>
       </c>
       <c r="L14" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N14" t="s">
         <v>256</v>
       </c>
       <c r="O14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W14" s="2">
         <v>46307</v>
@@ -2112,7 +2115,7 @@
         <v>261</v>
       </c>
       <c r="AA14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15" spans="1:27">
@@ -2147,10 +2150,10 @@
         <v>1</v>
       </c>
       <c r="K15">
-        <v>3554</v>
+        <v>3560</v>
       </c>
       <c r="L15" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M15" t="s">
         <v>263</v>
@@ -2159,19 +2162,19 @@
         <v>256</v>
       </c>
       <c r="O15" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P15" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q15" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R15" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W15" s="2">
-        <v>46304</v>
+        <v>46312</v>
       </c>
       <c r="Y15" t="s">
         <v>262</v>
@@ -2180,7 +2183,7 @@
         <v>261</v>
       </c>
       <c r="AA15" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="16" spans="1:27">
@@ -2218,7 +2221,7 @@
         <v>3609</v>
       </c>
       <c r="L16" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M16" t="s">
         <v>261</v>
@@ -2227,16 +2230,16 @@
         <v>256</v>
       </c>
       <c r="O16" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P16" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q16" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R16" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W16" s="2">
         <v>46308</v>
@@ -2248,7 +2251,7 @@
         <v>261</v>
       </c>
       <c r="AA16" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17" spans="1:27">
@@ -2280,37 +2283,37 @@
         <v>1</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17">
-        <v>1869</v>
+        <v>1872</v>
       </c>
       <c r="L17" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M17" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N17" t="s">
         <v>256</v>
       </c>
       <c r="O17" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q17" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W17" s="2">
-        <v>46113</v>
+        <v>46311</v>
       </c>
       <c r="AA17" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="18" spans="1:27">
@@ -2348,7 +2351,7 @@
         <v>3652</v>
       </c>
       <c r="L18" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M18" t="s">
         <v>261</v>
@@ -2357,16 +2360,16 @@
         <v>256</v>
       </c>
       <c r="O18" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P18" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q18" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R18" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W18" s="2">
         <v>46306</v>
@@ -2375,10 +2378,10 @@
         <v>262</v>
       </c>
       <c r="Z18" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AA18" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="19" spans="1:27">
@@ -2416,7 +2419,7 @@
         <v>125</v>
       </c>
       <c r="L19" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M19" t="s">
         <v>261</v>
@@ -2425,22 +2428,22 @@
         <v>256</v>
       </c>
       <c r="O19" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P19" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q19" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R19" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W19" s="2">
         <v>46163</v>
       </c>
       <c r="AA19" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="20" spans="1:27">
@@ -2487,16 +2490,16 @@
         <v>257</v>
       </c>
       <c r="O20" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P20" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q20" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R20" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W20" s="2">
         <v>46165</v>
@@ -2546,16 +2549,16 @@
         <v>257</v>
       </c>
       <c r="O21" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P21" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q21" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R21" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W21" s="2">
         <v>46166</v>
@@ -2596,7 +2599,7 @@
         <v>3591</v>
       </c>
       <c r="L22" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M22" t="s">
         <v>261</v>
@@ -2605,16 +2608,16 @@
         <v>256</v>
       </c>
       <c r="O22" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P22" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q22" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R22" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W22" s="2">
         <v>46168</v>
@@ -2626,7 +2629,7 @@
         <v>261</v>
       </c>
       <c r="AA22" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="23" spans="1:27">
@@ -2664,7 +2667,7 @@
         <v>3591</v>
       </c>
       <c r="L23" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M23" t="s">
         <v>261</v>
@@ -2673,16 +2676,16 @@
         <v>256</v>
       </c>
       <c r="O23" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P23" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q23" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R23" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W23" s="2">
         <v>46168</v>
@@ -2694,7 +2697,7 @@
         <v>261</v>
       </c>
       <c r="AA23" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="24" spans="1:27">
@@ -2732,7 +2735,7 @@
         <v>142</v>
       </c>
       <c r="L24" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M24" t="s">
         <v>261</v>
@@ -2741,16 +2744,16 @@
         <v>256</v>
       </c>
       <c r="O24" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P24" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q24" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R24" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W24" s="2">
         <v>46302</v>
@@ -2800,7 +2803,7 @@
         <v>164</v>
       </c>
       <c r="L25" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M25" t="s">
         <v>261</v>
@@ -2809,16 +2812,16 @@
         <v>256</v>
       </c>
       <c r="O25" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P25" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q25" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R25" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W25" s="2">
         <v>46307</v>
@@ -2830,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="AA25" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
     </row>
     <row r="26" spans="1:27">
@@ -2862,31 +2865,31 @@
         <v>1</v>
       </c>
       <c r="J26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L26" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M26" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N26" t="s">
         <v>256</v>
       </c>
       <c r="O26" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P26" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q26" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R26" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W26" s="2">
         <v>46307</v>
@@ -2898,7 +2901,7 @@
         <v>261</v>
       </c>
       <c r="AA26" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
     </row>
     <row r="27" spans="1:27">
@@ -2936,7 +2939,7 @@
         <v>2226</v>
       </c>
       <c r="L27" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M27" t="s">
         <v>261</v>
@@ -2945,22 +2948,22 @@
         <v>256</v>
       </c>
       <c r="O27" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P27" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q27" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R27" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W27" s="2">
         <v>46172</v>
       </c>
       <c r="AA27" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="28" spans="1:27">
@@ -2998,7 +3001,7 @@
         <v>2264</v>
       </c>
       <c r="L28" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M28" t="s">
         <v>261</v>
@@ -3007,22 +3010,22 @@
         <v>256</v>
       </c>
       <c r="O28" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P28" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q28" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R28" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W28" s="2">
         <v>46164</v>
       </c>
       <c r="AA28" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="29" spans="1:27">
@@ -3054,37 +3057,37 @@
         <v>1</v>
       </c>
       <c r="J29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29">
-        <v>1856</v>
+        <v>1858</v>
       </c>
       <c r="L29" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M29" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N29" t="s">
         <v>256</v>
       </c>
       <c r="O29" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P29" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q29" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R29" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W29" s="2">
         <v>46303.5896875</v>
       </c>
       <c r="AA29" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="30" spans="1:27">
@@ -3131,16 +3134,16 @@
         <v>257</v>
       </c>
       <c r="O30" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P30" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q30" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R30" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W30" s="2">
         <v>46168</v>
@@ -3190,16 +3193,16 @@
         <v>257</v>
       </c>
       <c r="O31" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P31" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q31" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R31" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W31" s="2">
         <v>46168</v>
@@ -3234,43 +3237,43 @@
         <v>1</v>
       </c>
       <c r="J32">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="K32">
-        <v>16539</v>
+        <v>17045</v>
       </c>
       <c r="L32" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M32" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="N32" t="s">
         <v>256</v>
       </c>
       <c r="O32" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P32" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q32" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R32" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W32" s="2">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="Y32" t="s">
         <v>262</v>
       </c>
       <c r="Z32" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AA32" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="33" spans="1:27">
@@ -3317,16 +3320,16 @@
         <v>257</v>
       </c>
       <c r="O33" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P33" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q33" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R33" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W33" s="2">
         <v>46168</v>
@@ -3376,16 +3379,16 @@
         <v>257</v>
       </c>
       <c r="O34" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P34" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q34" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R34" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W34" s="2">
         <v>46168</v>
@@ -3426,7 +3429,7 @@
         <v>3591</v>
       </c>
       <c r="L35" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M35" t="s">
         <v>261</v>
@@ -3435,16 +3438,16 @@
         <v>256</v>
       </c>
       <c r="O35" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P35" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q35" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R35" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W35" s="2">
         <v>46157</v>
@@ -3456,7 +3459,7 @@
         <v>261</v>
       </c>
       <c r="AA35" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="36" spans="1:27">
@@ -3494,7 +3497,7 @@
         <v>3591</v>
       </c>
       <c r="L36" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M36" t="s">
         <v>261</v>
@@ -3503,16 +3506,16 @@
         <v>256</v>
       </c>
       <c r="O36" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P36" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q36" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R36" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W36" s="2">
         <v>46168</v>
@@ -3524,7 +3527,7 @@
         <v>261</v>
       </c>
       <c r="AA36" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="37" spans="1:27">
@@ -3562,7 +3565,7 @@
         <v>1827</v>
       </c>
       <c r="L37" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M37" t="s">
         <v>261</v>
@@ -3571,16 +3574,16 @@
         <v>256</v>
       </c>
       <c r="O37" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P37" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q37" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R37" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W37" s="2">
         <v>46285</v>
@@ -3592,7 +3595,7 @@
         <v>261</v>
       </c>
       <c r="AA37" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="38" spans="1:27">
@@ -3630,7 +3633,7 @@
         <v>2937</v>
       </c>
       <c r="L38" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M38" t="s">
         <v>261</v>
@@ -3639,16 +3642,16 @@
         <v>256</v>
       </c>
       <c r="O38" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P38" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q38" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R38" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W38" s="2">
         <v>46113</v>
@@ -3660,7 +3663,7 @@
         <v>261</v>
       </c>
       <c r="AA38" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="39" spans="1:27">
@@ -3698,7 +3701,7 @@
         <v>3176</v>
       </c>
       <c r="L39" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M39" t="s">
         <v>261</v>
@@ -3707,16 +3710,16 @@
         <v>256</v>
       </c>
       <c r="O39" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P39" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q39" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R39" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W39" s="2">
         <v>46140</v>
@@ -3728,7 +3731,7 @@
         <v>261</v>
       </c>
       <c r="AA39" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="40" spans="1:27">
@@ -3766,7 +3769,7 @@
         <v>3128</v>
       </c>
       <c r="L40" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M40" t="s">
         <v>261</v>
@@ -3775,16 +3778,16 @@
         <v>256</v>
       </c>
       <c r="O40" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P40" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q40" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R40" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W40" s="2">
         <v>46024</v>
@@ -3796,7 +3799,7 @@
         <v>261</v>
       </c>
       <c r="AA40" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="41" spans="1:27">
@@ -3834,7 +3837,7 @@
         <v>3542</v>
       </c>
       <c r="L41" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M41" t="s">
         <v>261</v>
@@ -3843,16 +3846,16 @@
         <v>256</v>
       </c>
       <c r="O41" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P41" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q41" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R41" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W41" s="2">
         <v>46168</v>
@@ -3864,7 +3867,7 @@
         <v>261</v>
       </c>
       <c r="AA41" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="42" spans="1:27">
@@ -3902,7 +3905,7 @@
         <v>3533</v>
       </c>
       <c r="L42" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M42" t="s">
         <v>261</v>
@@ -3911,16 +3914,16 @@
         <v>256</v>
       </c>
       <c r="O42" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P42" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q42" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R42" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W42" s="2">
         <v>46164</v>
@@ -3932,7 +3935,7 @@
         <v>261</v>
       </c>
       <c r="AA42" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="43" spans="1:27">
@@ -3970,7 +3973,7 @@
         <v>3513</v>
       </c>
       <c r="L43" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M43" t="s">
         <v>261</v>
@@ -3979,16 +3982,16 @@
         <v>256</v>
       </c>
       <c r="O43" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P43" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q43" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R43" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W43" s="2">
         <v>46112</v>
@@ -4000,7 +4003,7 @@
         <v>261</v>
       </c>
       <c r="AA43" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="44" spans="1:27">
@@ -4047,16 +4050,16 @@
         <v>257</v>
       </c>
       <c r="O44" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P44" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q44" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R44" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W44" s="2">
         <v>46171</v>
@@ -4091,13 +4094,13 @@
         <v>1</v>
       </c>
       <c r="J45">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K45">
-        <v>3913</v>
+        <v>3992</v>
       </c>
       <c r="L45" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M45" t="s">
         <v>262</v>
@@ -4106,19 +4109,19 @@
         <v>256</v>
       </c>
       <c r="O45" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P45" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q45" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R45" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W45" s="2">
-        <v>46308</v>
+        <v>46311</v>
       </c>
       <c r="Y45" t="s">
         <v>262</v>
@@ -4127,7 +4130,7 @@
         <v>261</v>
       </c>
       <c r="AA45" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="46" spans="1:27">
@@ -4159,13 +4162,13 @@
         <v>1</v>
       </c>
       <c r="J46">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="K46">
-        <v>10508</v>
+        <v>10791</v>
       </c>
       <c r="L46" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M46" t="s">
         <v>262</v>
@@ -4174,19 +4177,19 @@
         <v>256</v>
       </c>
       <c r="O46" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P46" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q46" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R46" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W46" s="2">
-        <v>46308</v>
+        <v>46311</v>
       </c>
       <c r="Y46" t="s">
         <v>262</v>
@@ -4195,7 +4198,7 @@
         <v>261</v>
       </c>
       <c r="AA46" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="47" spans="1:27">
@@ -4227,13 +4230,13 @@
         <v>1</v>
       </c>
       <c r="J47">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K47">
-        <v>4916</v>
+        <v>5056</v>
       </c>
       <c r="L47" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M47" t="s">
         <v>262</v>
@@ -4242,19 +4245,19 @@
         <v>256</v>
       </c>
       <c r="O47" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P47" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q47" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R47" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W47" s="2">
-        <v>46308</v>
+        <v>46311</v>
       </c>
       <c r="Y47" t="s">
         <v>262</v>
@@ -4263,7 +4266,7 @@
         <v>261</v>
       </c>
       <c r="AA47" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="48" spans="1:27">
@@ -4301,7 +4304,7 @@
         <v>2299</v>
       </c>
       <c r="L48" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M48" t="s">
         <v>261</v>
@@ -4310,16 +4313,16 @@
         <v>256</v>
       </c>
       <c r="O48" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P48" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q48" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R48" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W48" s="2">
         <v>46168</v>
@@ -4331,7 +4334,7 @@
         <v>261</v>
       </c>
       <c r="AA48" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="49" spans="1:27">
@@ -4363,34 +4366,34 @@
         <v>1</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K49">
-        <v>1515</v>
+        <v>1521</v>
       </c>
       <c r="L49" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M49" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N49" t="s">
         <v>256</v>
       </c>
       <c r="O49" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P49" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q49" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R49" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W49" s="2">
-        <v>46288</v>
+        <v>46311</v>
       </c>
       <c r="Y49" t="s">
         <v>262</v>
@@ -4399,7 +4402,7 @@
         <v>261</v>
       </c>
       <c r="AA49" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="50" spans="1:27">
@@ -4431,34 +4434,34 @@
         <v>1</v>
       </c>
       <c r="J50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K50">
-        <v>1793</v>
+        <v>1813</v>
       </c>
       <c r="L50" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M50" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N50" t="s">
         <v>256</v>
       </c>
       <c r="O50" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P50" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q50" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R50" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W50" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="Y50" t="s">
         <v>262</v>
@@ -4467,7 +4470,7 @@
         <v>261</v>
       </c>
       <c r="AA50" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="51" spans="1:27">
@@ -4499,31 +4502,31 @@
         <v>1</v>
       </c>
       <c r="J51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="L51" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M51" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N51" t="s">
         <v>256</v>
       </c>
       <c r="O51" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P51" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q51" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R51" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W51" s="2">
         <v>46307</v>
@@ -4535,7 +4538,7 @@
         <v>261</v>
       </c>
       <c r="AA51" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="52" spans="1:27">
@@ -4573,7 +4576,7 @@
         <v>1473</v>
       </c>
       <c r="L52" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M52" t="s">
         <v>261</v>
@@ -4582,16 +4585,16 @@
         <v>256</v>
       </c>
       <c r="O52" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P52" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q52" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R52" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W52" s="2">
         <v>46306</v>
@@ -4603,7 +4606,7 @@
         <v>261</v>
       </c>
       <c r="AA52" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="53" spans="1:27">
@@ -4641,7 +4644,7 @@
         <v>2217</v>
       </c>
       <c r="L53" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M53" t="s">
         <v>261</v>
@@ -4650,16 +4653,16 @@
         <v>256</v>
       </c>
       <c r="O53" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P53" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q53" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R53" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W53" s="2">
         <v>46302</v>
@@ -4671,7 +4674,7 @@
         <v>261</v>
       </c>
       <c r="AA53" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="54" spans="1:27">
@@ -4709,7 +4712,7 @@
         <v>1396</v>
       </c>
       <c r="L54" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M54" t="s">
         <v>261</v>
@@ -4718,16 +4721,16 @@
         <v>256</v>
       </c>
       <c r="O54" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P54" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q54" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R54" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W54" s="2">
         <v>46302</v>
@@ -4739,7 +4742,7 @@
         <v>261</v>
       </c>
       <c r="AA54" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="55" spans="1:27">
@@ -4771,43 +4774,43 @@
         <v>1</v>
       </c>
       <c r="J55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K55">
-        <v>2564</v>
+        <v>2578</v>
       </c>
       <c r="L55" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M55" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N55" t="s">
         <v>256</v>
       </c>
       <c r="O55" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P55" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q55" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R55" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W55" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="Y55" t="s">
         <v>262</v>
       </c>
       <c r="Z55" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AA55" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="56" spans="1:27">
@@ -4854,16 +4857,16 @@
         <v>257</v>
       </c>
       <c r="O56" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P56" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q56" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R56" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W56" s="2">
         <v>46161</v>
@@ -4898,31 +4901,31 @@
         <v>1</v>
       </c>
       <c r="J57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K57">
-        <v>4012</v>
+        <v>4016</v>
       </c>
       <c r="L57" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M57" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N57" t="s">
         <v>256</v>
       </c>
       <c r="O57" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P57" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q57" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R57" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W57" s="2">
         <v>46307</v>
@@ -4934,7 +4937,7 @@
         <v>261</v>
       </c>
       <c r="AA57" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="58" spans="1:27">
@@ -4981,16 +4984,16 @@
         <v>257</v>
       </c>
       <c r="O58" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P58" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q58" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R58" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W58" s="2">
         <v>46148</v>
@@ -5040,16 +5043,16 @@
         <v>257</v>
       </c>
       <c r="O59" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P59" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q59" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R59" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W59" s="2">
         <v>46168</v>
@@ -5099,16 +5102,16 @@
         <v>257</v>
       </c>
       <c r="O60" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P60" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q60" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R60" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W60" s="2">
         <v>46164</v>
@@ -5158,16 +5161,16 @@
         <v>257</v>
       </c>
       <c r="O61" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P61" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q61" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R61" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W61" s="2">
         <v>46168</v>
@@ -5202,34 +5205,34 @@
         <v>1</v>
       </c>
       <c r="J62">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K62">
-        <v>1681</v>
+        <v>1687</v>
       </c>
       <c r="L62" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M62" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N62" t="s">
         <v>256</v>
       </c>
       <c r="O62" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P62" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q62" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R62" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W62" s="2">
-        <v>46288</v>
+        <v>46311</v>
       </c>
       <c r="Y62" t="s">
         <v>262</v>
@@ -5238,7 +5241,7 @@
         <v>261</v>
       </c>
       <c r="AA62" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="63" spans="1:27">
@@ -5285,16 +5288,16 @@
         <v>257</v>
       </c>
       <c r="O63" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P63" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q63" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R63" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W63" s="2">
         <v>46164</v>
@@ -5344,16 +5347,16 @@
         <v>257</v>
       </c>
       <c r="O64" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P64" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q64" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R64" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W64" s="2">
         <v>46168</v>
@@ -5388,13 +5391,13 @@
         <v>1</v>
       </c>
       <c r="J65">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="K65">
-        <v>4963</v>
+        <v>5083</v>
       </c>
       <c r="L65" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M65" t="s">
         <v>262</v>
@@ -5403,28 +5406,28 @@
         <v>256</v>
       </c>
       <c r="O65" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P65" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q65" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R65" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W65" s="2">
-        <v>46308</v>
+        <v>46311</v>
       </c>
       <c r="Y65" t="s">
         <v>262</v>
       </c>
       <c r="Z65" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AA65" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="66" spans="1:27">
@@ -5462,7 +5465,7 @@
         <v>3062</v>
       </c>
       <c r="L66" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M66" t="s">
         <v>261</v>
@@ -5471,16 +5474,16 @@
         <v>256</v>
       </c>
       <c r="O66" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P66" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q66" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R66" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W66" s="2">
         <v>46261</v>
@@ -5492,7 +5495,7 @@
         <v>261</v>
       </c>
       <c r="AA66" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="67" spans="1:27">
@@ -5527,10 +5530,10 @@
         <v>1</v>
       </c>
       <c r="K67">
-        <v>1776</v>
+        <v>1785</v>
       </c>
       <c r="L67" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M67" t="s">
         <v>263</v>
@@ -5539,28 +5542,28 @@
         <v>256</v>
       </c>
       <c r="O67" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P67" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q67" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R67" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W67" s="2">
-        <v>46308</v>
+        <v>46311</v>
       </c>
       <c r="Y67" t="s">
         <v>262</v>
       </c>
       <c r="Z67" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AA67" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="68" spans="1:27">
@@ -5592,13 +5595,13 @@
         <v>1</v>
       </c>
       <c r="J68">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K68">
-        <v>4529</v>
+        <v>4576</v>
       </c>
       <c r="L68" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M68" t="s">
         <v>262</v>
@@ -5607,28 +5610,28 @@
         <v>256</v>
       </c>
       <c r="O68" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P68" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q68" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R68" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W68" s="2">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="Y68" t="s">
         <v>262</v>
       </c>
       <c r="Z68" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AA68" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="69" spans="1:27">
@@ -5666,7 +5669,7 @@
         <v>3069</v>
       </c>
       <c r="L69" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M69" t="s">
         <v>261</v>
@@ -5675,16 +5678,16 @@
         <v>256</v>
       </c>
       <c r="O69" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P69" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q69" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R69" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W69" s="2">
         <v>46280</v>
@@ -5696,7 +5699,7 @@
         <v>261</v>
       </c>
       <c r="AA69" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="70" spans="1:27">
@@ -5728,43 +5731,43 @@
         <v>1</v>
       </c>
       <c r="J70">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K70">
-        <v>2827</v>
+        <v>2851</v>
       </c>
       <c r="L70" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M70" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N70" t="s">
         <v>256</v>
       </c>
       <c r="O70" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P70" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q70" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R70" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W70" s="2">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="Y70" t="s">
         <v>262</v>
       </c>
       <c r="Z70" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AA70" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="71" spans="1:27">
@@ -5796,31 +5799,31 @@
         <v>1</v>
       </c>
       <c r="J71">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K71">
-        <v>2854</v>
+        <v>2864</v>
       </c>
       <c r="L71" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M71" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N71" t="s">
         <v>256</v>
       </c>
       <c r="O71" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P71" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q71" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R71" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W71" s="2">
         <v>46308</v>
@@ -5829,10 +5832,10 @@
         <v>262</v>
       </c>
       <c r="Z71" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AA71" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="72" spans="1:27">
@@ -5879,16 +5882,16 @@
         <v>257</v>
       </c>
       <c r="O72" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P72" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q72" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R72" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W72" s="2">
         <v>46164</v>
@@ -5929,7 +5932,7 @@
         <v>1393</v>
       </c>
       <c r="L73" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M73" t="s">
         <v>261</v>
@@ -5938,16 +5941,16 @@
         <v>256</v>
       </c>
       <c r="O73" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P73" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q73" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R73" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W73" s="2">
         <v>46301</v>
@@ -5959,7 +5962,7 @@
         <v>261</v>
       </c>
       <c r="AA73" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="74" spans="1:27">
@@ -5997,7 +6000,7 @@
         <v>1449</v>
       </c>
       <c r="L74" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M74" t="s">
         <v>261</v>
@@ -6006,16 +6009,16 @@
         <v>256</v>
       </c>
       <c r="O74" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P74" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q74" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R74" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W74" s="2">
         <v>46185</v>
@@ -6027,7 +6030,7 @@
         <v>261</v>
       </c>
       <c r="AA74" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="75" spans="1:27">
@@ -6065,7 +6068,7 @@
         <v>1482</v>
       </c>
       <c r="L75" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M75" t="s">
         <v>261</v>
@@ -6074,16 +6077,16 @@
         <v>256</v>
       </c>
       <c r="O75" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P75" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q75" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R75" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W75" s="2">
         <v>46265</v>
@@ -6095,7 +6098,7 @@
         <v>261</v>
       </c>
       <c r="AA75" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="76" spans="1:27">
@@ -6133,7 +6136,7 @@
         <v>1546</v>
       </c>
       <c r="L76" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M76" t="s">
         <v>261</v>
@@ -6142,16 +6145,16 @@
         <v>256</v>
       </c>
       <c r="O76" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P76" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q76" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R76" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W76" s="2">
         <v>46303</v>
@@ -6163,7 +6166,7 @@
         <v>261</v>
       </c>
       <c r="AA76" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="77" spans="1:27">
@@ -6201,7 +6204,7 @@
         <v>1581</v>
       </c>
       <c r="L77" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M77" t="s">
         <v>261</v>
@@ -6210,16 +6213,16 @@
         <v>256</v>
       </c>
       <c r="O77" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P77" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q77" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R77" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W77" s="2">
         <v>46301</v>
@@ -6231,7 +6234,7 @@
         <v>261</v>
       </c>
       <c r="AA77" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="78" spans="1:27">
@@ -6263,34 +6266,34 @@
         <v>1</v>
       </c>
       <c r="J78">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K78">
-        <v>1580</v>
+        <v>1586</v>
       </c>
       <c r="L78" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M78" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N78" t="s">
         <v>256</v>
       </c>
       <c r="O78" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P78" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q78" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R78" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W78" s="2">
-        <v>46288</v>
+        <v>46311</v>
       </c>
       <c r="Y78" t="s">
         <v>262</v>
@@ -6299,7 +6302,7 @@
         <v>261</v>
       </c>
       <c r="AA78" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="79" spans="1:27">
@@ -6331,13 +6334,13 @@
         <v>1</v>
       </c>
       <c r="J79">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K79">
-        <v>1902</v>
+        <v>1944</v>
       </c>
       <c r="L79" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M79" t="s">
         <v>262</v>
@@ -6346,19 +6349,19 @@
         <v>256</v>
       </c>
       <c r="O79" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P79" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q79" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R79" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W79" s="2">
-        <v>46308</v>
+        <v>46311</v>
       </c>
       <c r="Y79" t="s">
         <v>262</v>
@@ -6367,7 +6370,7 @@
         <v>261</v>
       </c>
       <c r="AA79" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="80" spans="1:27">
@@ -6405,7 +6408,7 @@
         <v>1632</v>
       </c>
       <c r="L80" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M80" t="s">
         <v>261</v>
@@ -6414,16 +6417,16 @@
         <v>256</v>
       </c>
       <c r="O80" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P80" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q80" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R80" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W80" s="2">
         <v>46305</v>
@@ -6435,7 +6438,7 @@
         <v>261</v>
       </c>
       <c r="AA80" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="81" spans="1:27">
@@ -6473,7 +6476,7 @@
         <v>3591</v>
       </c>
       <c r="L81" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M81" t="s">
         <v>261</v>
@@ -6482,16 +6485,16 @@
         <v>256</v>
       </c>
       <c r="O81" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P81" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q81" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R81" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W81" s="2">
         <v>46160</v>
@@ -6503,7 +6506,7 @@
         <v>261</v>
       </c>
       <c r="AA81" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="82" spans="1:27">
@@ -6541,7 +6544,7 @@
         <v>2137</v>
       </c>
       <c r="L82" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M82" t="s">
         <v>261</v>
@@ -6550,22 +6553,22 @@
         <v>256</v>
       </c>
       <c r="O82" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P82" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q82" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R82" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W82" s="2">
         <v>46161</v>
       </c>
       <c r="AA82" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="83" spans="1:27">
@@ -6597,37 +6600,37 @@
         <v>1</v>
       </c>
       <c r="J83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K83">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="L83" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M83" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N83" t="s">
         <v>256</v>
       </c>
       <c r="O83" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P83" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q83" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R83" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W83" s="2">
-        <v>46168</v>
+        <v>46311</v>
       </c>
       <c r="AA83" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="84" spans="1:27">
@@ -6674,16 +6677,16 @@
         <v>257</v>
       </c>
       <c r="O84" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P84" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q84" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R84" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W84" s="2">
         <v>46164</v>
@@ -6733,16 +6736,16 @@
         <v>257</v>
       </c>
       <c r="O85" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P85" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q85" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R85" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W85" s="2">
         <v>46168</v>
@@ -6783,7 +6786,7 @@
         <v>652</v>
       </c>
       <c r="L86" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M86" t="s">
         <v>261</v>
@@ -6792,16 +6795,16 @@
         <v>256</v>
       </c>
       <c r="O86" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P86" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q86" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R86" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W86" s="2">
         <v>46164</v>
@@ -6813,7 +6816,7 @@
         <v>261</v>
       </c>
       <c r="AA86" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="87" spans="1:27">
@@ -6851,7 +6854,7 @@
         <v>3617</v>
       </c>
       <c r="L87" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M87" t="s">
         <v>261</v>
@@ -6860,16 +6863,16 @@
         <v>256</v>
       </c>
       <c r="O87" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P87" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q87" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R87" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W87" s="2">
         <v>46303</v>
@@ -6881,7 +6884,7 @@
         <v>261</v>
       </c>
       <c r="AA87" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="88" spans="1:27">
@@ -6919,7 +6922,7 @@
         <v>3580</v>
       </c>
       <c r="L88" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M88" t="s">
         <v>261</v>
@@ -6928,16 +6931,16 @@
         <v>256</v>
       </c>
       <c r="O88" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P88" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q88" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R88" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W88" s="2">
         <v>46253.16666666666</v>
@@ -6949,7 +6952,7 @@
         <v>261</v>
       </c>
       <c r="AA88" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="89" spans="1:27">
@@ -6981,16 +6984,16 @@
         <v>257</v>
       </c>
       <c r="O89" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P89" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q89" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R89" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="90" spans="1:27">
@@ -7022,13 +7025,13 @@
         <v>1</v>
       </c>
       <c r="J90">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K90">
-        <v>129</v>
+        <v>177</v>
       </c>
       <c r="L90" s="2">
-        <v>46309.20672453703</v>
+        <v>46313.29368055556</v>
       </c>
       <c r="M90" t="s">
         <v>262</v>
@@ -7037,19 +7040,19 @@
         <v>256</v>
       </c>
       <c r="O90" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P90" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q90" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R90" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W90" s="2">
-        <v>46304</v>
+        <v>46311</v>
       </c>
       <c r="Y90" t="s">
         <v>262</v>
@@ -7058,7 +7061,7 @@
         <v>261</v>
       </c>
       <c r="AA90" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="91" spans="1:27">
@@ -7090,16 +7093,16 @@
         <v>256</v>
       </c>
       <c r="O91" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P91" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q91" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R91" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W91" s="2">
         <v>46154</v>
@@ -7149,16 +7152,16 @@
         <v>257</v>
       </c>
       <c r="O92" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P92" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q92" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R92" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W92" s="2">
         <v>46164</v>
